--- a/proyectos/Proyecto_Master_Data_Quality/maestro de articulos para porfolio.xlsx
+++ b/proyectos/Proyecto_Master_Data_Quality/maestro de articulos para porfolio.xlsx
@@ -4,15 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13980"/>
+    <workbookView windowWidth="28800" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="maestro " sheetId="1" r:id="rId1"/>
+    <sheet name="Analisis" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$BW$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Analisis!$A$12:$D$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'maestro '!$A$1:$BW$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="204">
   <si>
     <t>Codigo</t>
   </si>
@@ -492,6 +497,156 @@
   </si>
   <si>
     <t>Bee 24 - Unidad Ext. Frio/Calor</t>
+  </si>
+  <si>
+    <t>Métrica</t>
+  </si>
+  <si>
+    <t>Fórmula utilizada</t>
+  </si>
+  <si>
+    <t>resultado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interpretacion </t>
+  </si>
+  <si>
+    <t>Total registros</t>
+  </si>
+  <si>
+    <t>=FILAS('maestro '!b1:BW35)'</t>
+  </si>
+  <si>
+    <t>tamaño del DataSet</t>
+  </si>
+  <si>
+    <t>Total columnas</t>
+  </si>
+  <si>
+    <t>=COLUMNAS('maestro '!A1:BW36)'</t>
+  </si>
+  <si>
+    <t>Cantidad de Atributos</t>
+  </si>
+  <si>
+    <t>Celdas totales</t>
+  </si>
+  <si>
+    <t>Registros * Columnas'</t>
+  </si>
+  <si>
+    <t>Cantidad Celdas analizadas</t>
+  </si>
+  <si>
+    <t>Celdas vacías</t>
+  </si>
+  <si>
+    <t>=CONTAR.BLANCO(maestro '!A2:BW35)'</t>
+  </si>
+  <si>
+    <t>Sin Informacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celdas con informacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celdas totales - Celdas vacias </t>
+  </si>
+  <si>
+    <t>Con informacion</t>
+  </si>
+  <si>
+    <t>% Indice Cobertura de Datos</t>
+  </si>
+  <si>
+    <t>Celdas con informacion /Celdas totales '</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porcentaje de informacion presente  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevancia de los Atributos </t>
+  </si>
+  <si>
+    <t>Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categoria </t>
+  </si>
+  <si>
+    <t>Relevancia  operativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificación del Material </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critico </t>
+  </si>
+  <si>
+    <t>Estos campos permiten identificar de forma única el artículo.</t>
+  </si>
+  <si>
+    <t>Clasificación del Material</t>
+  </si>
+  <si>
+    <t>Permiten agrupar y analizar productos.</t>
+  </si>
+  <si>
+    <t>Operación e Interfaces</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Campos usados para integración entre sistemas.</t>
+  </si>
+  <si>
+    <t>Inventario y Reposición</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Ayudan a gestionar stock.</t>
+  </si>
+  <si>
+    <t>Logística y Dimensiones</t>
+  </si>
+  <si>
+    <t>Fundamentales para almacenamiento y transporte.</t>
+  </si>
+  <si>
+    <t>Palletizado</t>
+  </si>
+  <si>
+    <t>Información necesaria para almacenamiento masivo.</t>
+  </si>
+  <si>
+    <t>Financiera</t>
+  </si>
+  <si>
+    <t>Importantes para valorización.</t>
+  </si>
+  <si>
+    <t>Organización y Cliente</t>
+  </si>
+  <si>
+    <t>Relacionan el artículo con la estructura empresarial.</t>
+  </si>
+  <si>
+    <t>Campos Personalizados</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uso interno </t>
+  </si>
+  <si>
+    <t>Recuento de Relevancia  operativa</t>
+  </si>
+  <si>
+    <t>Total general</t>
   </si>
 </sst>
 </file>
@@ -505,8 +660,29 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -852,12 +1028,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -978,142 +1169,193 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1390,6 +1632,760 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46175.7271296296" refreshedBy="PAPA" recordCount="75">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A12:D87" sheet="Analisis"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Campo" numFmtId="0">
+      <sharedItems count="74">
+        <s v="Codigo"/>
+        <s v="Codigo_Producto_Sistema"/>
+        <s v="Codigo_Tipo_Producto"/>
+        <s v="Codigo_Familia"/>
+        <s v="Codigo_Tipo_Entrada"/>
+        <s v="Codigo_Tipo_Salida"/>
+        <s v="Codigo_Categoria_Producto"/>
+        <s v="Codigo_SubZona_Almacen"/>
+        <s v="Nombre"/>
+        <s v="Descripcion"/>
+        <s v="Codigo_Barra"/>
+        <s v="Codigo_Barra_Secundario"/>
+        <s v="Codigo_UM_Vol"/>
+        <s v="Volumen_Neto"/>
+        <s v="Volumen_Bruto"/>
+        <s v="Codigo_UM_Peso"/>
+        <s v="Peso_Neto"/>
+        <s v="Peso_Bruto"/>
+        <s v="Codigo_UM_Dimension"/>
+        <s v="Altura"/>
+        <s v="Ancho"/>
+        <s v="Profundidad"/>
+        <s v="Codigo_UM_Presentacion_Defecto"/>
+        <s v="Codigo_Pallet_Por_Defecto"/>
+        <s v="Codigo_UM_Palletizado"/>
+        <s v="Codigo_UM_Peso_Pallets"/>
+        <s v="Peso_Pallet"/>
+        <s v="Codigo_UM_Dimension_Pallets"/>
+        <s v="Altura_Pallet"/>
+        <s v="Ancho_Pallet"/>
+        <s v="Profundidad_Pallet"/>
+        <s v="Codigo_Secundario"/>
+        <s v="Stock_Minimo_Reposicion"/>
+        <s v="Stock_Minimo_Reubicacion"/>
+        <s v="Codigo_UM_Moneda"/>
+        <s v="Valor_Comercial"/>
+        <s v="Valor_Asegurado"/>
+        <s v="Valor_Costo"/>
+        <s v="Tasa_Cambio"/>
+        <s v="Coef_Unidad_Almacenamiento"/>
+        <s v="Codigo_Cliente"/>
+        <s v="nombre_Cliente"/>
+        <s v="Codigo_Empresa"/>
+        <s v="Codigo_Empresa_Sector"/>
+        <s v="CDXU_Num1"/>
+        <s v="CDXU_Num2"/>
+        <s v="CDXU_Num3"/>
+        <s v="CDXU_Num4"/>
+        <s v="CDXU_Alf_Corto1"/>
+        <s v="CDXU_Alf_Corto2"/>
+        <s v="CDXU_Alf_Corto3"/>
+        <s v="CDXU_Alf_Corto4"/>
+        <s v="CDXU_Alf_Largo1"/>
+        <s v="CDXU_Alf_Largo2"/>
+        <s v="CDXU_Alf_Largo3"/>
+        <s v="CDXU_Alf_Largo4"/>
+        <s v="CDXU_Fecha1"/>
+        <s v="CDXU_Fecha2"/>
+        <s v="CDXU_Fecha3"/>
+        <s v="CDXU_Fecha4"/>
+        <s v="CDXU_Bit1"/>
+        <s v="CDXU_Bit2"/>
+        <s v="CDXU_Bit3"/>
+        <s v="CDXU_Bit4"/>
+        <s v="Codigo_Talle_Cab"/>
+        <s v="Codigo_Color_Cab"/>
+        <s v="Codigo_Sabor_Cab"/>
+        <s v="Codigo_Fragancia_Cab"/>
+        <s v="Codigo_Atrib1_Cab"/>
+        <s v="Codigo_Atrib2_Cab"/>
+        <s v="Sistema Destino"/>
+        <s v="Acción (Agregar &quot;A&quot; , Modificar &quot;M&quot;, Baja &quot;B&quot;)"/>
+        <s v="CompaniaDestino"/>
+        <s v="Id_subzona"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="categoria " numFmtId="0">
+      <sharedItems count="9">
+        <s v="Identificación del Material "/>
+        <s v="Clasificación del Material"/>
+        <s v="Operación e Interfaces"/>
+        <s v="Inventario y Reposición"/>
+        <s v="Logística y Dimensiones"/>
+        <s v="Palletizado"/>
+        <s v="Financiera"/>
+        <s v="Organización y Cliente"/>
+        <s v="Campos Personalizados"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Relevancia  operativa" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Critico "/>
+        <s v="Media"/>
+        <s v="Alta"/>
+        <s v="Baja"/>
+        <m u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Descripcion" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Estos campos permiten identificar de forma única el artículo."/>
+        <s v="Permiten agrupar y analizar productos."/>
+        <s v="Campos usados para integración entre sistemas."/>
+        <s v="Ayudan a gestionar stock."/>
+        <s v="Fundamentales para almacenamiento y transporte."/>
+        <s v="Información necesaria para almacenamiento masivo."/>
+        <s v="Importantes para valorización."/>
+        <s v="Relacionan el artículo con la estructura empresarial."/>
+        <s v="uso interno "/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="75">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabla _x000a_dinámica2" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
+  <location ref="A90:F101" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField compact="0" showAll="0">
+      <items count="75">
+        <item x="71"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item x="29"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="0"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="40"/>
+        <item x="65"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="3"/>
+        <item x="67"/>
+        <item x="23"/>
+        <item x="1"/>
+        <item x="66"/>
+        <item x="31"/>
+        <item x="7"/>
+        <item x="64"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="27"/>
+        <item x="34"/>
+        <item x="24"/>
+        <item x="15"/>
+        <item x="25"/>
+        <item x="22"/>
+        <item x="12"/>
+        <item x="39"/>
+        <item x="72"/>
+        <item x="9"/>
+        <item x="73"/>
+        <item x="8"/>
+        <item x="41"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="26"/>
+        <item x="21"/>
+        <item x="30"/>
+        <item x="70"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="37"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" dataField="1" compact="0" sortType="ascending" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item m="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Recuento de Relevancia  operativa" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1645,8 +2641,61 @@
   <cols>
     <col min="1" max="1" width="15.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="26.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="19.2857142857143" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.8571428571429" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="15.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="26.8571428571429" customWidth="1"/>
+    <col min="9" max="10" width="37.5714285714286" customWidth="1"/>
+    <col min="11" max="11" width="15.5714285714286" style="17" customWidth="1"/>
+    <col min="12" max="12" width="25.8571428571429" style="17" customWidth="1"/>
+    <col min="13" max="13" width="16.4285714285714" customWidth="1"/>
+    <col min="14" max="14" width="15.7142857142857" customWidth="1"/>
+    <col min="15" max="15" width="16.2857142857143" customWidth="1"/>
+    <col min="16" max="16" width="17.8571428571429" customWidth="1"/>
+    <col min="17" max="17" width="11.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.8571428571429" customWidth="1"/>
+    <col min="19" max="19" width="23.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="7.14285714285714" customWidth="1"/>
+    <col min="22" max="22" width="12.8571428571429" customWidth="1"/>
+    <col min="23" max="23" width="35" customWidth="1"/>
+    <col min="24" max="24" width="27.8571428571429" customWidth="1"/>
+    <col min="25" max="25" width="24.1428571428571" customWidth="1"/>
+    <col min="26" max="26" width="25.7142857142857" customWidth="1"/>
+    <col min="27" max="27" width="12.2857142857143" customWidth="1"/>
+    <col min="28" max="28" width="31.7142857142857" customWidth="1"/>
+    <col min="29" max="29" width="13.5714285714286" customWidth="1"/>
+    <col min="30" max="30" width="13.7142857142857" customWidth="1"/>
+    <col min="31" max="31" width="19.8571428571429" customWidth="1"/>
+    <col min="32" max="32" width="19.5714285714286" customWidth="1"/>
+    <col min="33" max="33" width="26.7142857142857" customWidth="1"/>
+    <col min="34" max="34" width="27.8571428571429" customWidth="1"/>
+    <col min="35" max="35" width="21.2857142857143" customWidth="1"/>
+    <col min="36" max="36" width="16.8571428571429" customWidth="1"/>
+    <col min="37" max="37" width="17.5714285714286" customWidth="1"/>
+    <col min="38" max="38" width="12.5714285714286" customWidth="1"/>
+    <col min="39" max="39" width="13.5714285714286" customWidth="1"/>
+    <col min="40" max="40" width="31.5714285714286" customWidth="1"/>
+    <col min="41" max="42" width="15.7142857142857" customWidth="1"/>
+    <col min="43" max="43" width="21.2857142857143" customWidth="1"/>
+    <col min="44" max="44" width="17" customWidth="1"/>
+    <col min="45" max="45" width="24.4285714285714" customWidth="1"/>
+    <col min="46" max="49" width="13" customWidth="1"/>
+    <col min="50" max="53" width="17.7142857142857" customWidth="1"/>
+    <col min="54" max="57" width="17.5714285714286" customWidth="1"/>
+    <col min="58" max="61" width="14" customWidth="1"/>
+    <col min="62" max="65" width="11" customWidth="1"/>
+    <col min="66" max="66" width="18.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="18.7142857142857" customWidth="1"/>
+    <col min="68" max="68" width="19" customWidth="1"/>
+    <col min="69" max="69" width="22.7142857142857" customWidth="1"/>
+    <col min="70" max="71" width="19.4285714285714" customWidth="1"/>
+    <col min="72" max="72" width="16.5714285714286" customWidth="1"/>
+    <col min="73" max="73" width="45.1428571428571" customWidth="1"/>
+    <col min="74" max="74" width="20" customWidth="1"/>
+    <col min="75" max="75" width="11.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:75">
@@ -1680,10 +2729,10 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1901,10 +2950,10 @@
       <c r="J2" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="17">
         <v>7798083661333</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="17">
         <v>7798083661333</v>
       </c>
       <c r="M2" t="s">
@@ -1987,10 +3036,10 @@
       <c r="J3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="17">
         <v>7798083661340</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="17">
         <v>7798083661340</v>
       </c>
       <c r="M3" t="s">
@@ -2073,10 +3122,10 @@
       <c r="J4" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="17">
         <v>7798083661173</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="17">
         <v>7798083661173</v>
       </c>
       <c r="M4" t="s">
@@ -2159,10 +3208,10 @@
       <c r="J5" t="s">
         <v>95</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="17">
         <v>7798083661364</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="17">
         <v>7798083661364</v>
       </c>
       <c r="M5" t="s">
@@ -2245,10 +3294,10 @@
       <c r="J6" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="17">
         <v>7798083661371</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="17">
         <v>7798083661371</v>
       </c>
       <c r="M6" t="s">
@@ -2331,10 +3380,10 @@
       <c r="J7" t="s">
         <v>99</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="17">
         <v>7798083661210</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="17">
         <v>7798083661210</v>
       </c>
       <c r="M7" t="s">
@@ -2417,10 +3466,10 @@
       <c r="J8" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="17">
         <v>7798083661517</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="17">
         <v>7798083661517</v>
       </c>
       <c r="M8" t="s">
@@ -2503,10 +3552,10 @@
       <c r="J9" t="s">
         <v>103</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="17">
         <v>7798083661524</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="17">
         <v>7798083661524</v>
       </c>
       <c r="M9" t="s">
@@ -2589,10 +3638,10 @@
       <c r="J10" t="s">
         <v>107</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="17">
         <v>7792004000145</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="17">
         <v>7792004000145</v>
       </c>
       <c r="M10" t="s">
@@ -2675,10 +3724,10 @@
       <c r="J11" t="s">
         <v>111</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="17">
         <v>7792006000124</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="17">
         <v>7792006000124</v>
       </c>
       <c r="M11" t="s">
@@ -2761,10 +3810,10 @@
       <c r="J12" t="s">
         <v>111</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="17">
         <v>7792006000124</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="17">
         <v>7792006000124</v>
       </c>
       <c r="M12" t="s">
@@ -2847,10 +3896,10 @@
       <c r="J13" t="s">
         <v>111</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="17">
         <v>7792006000124</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="17">
         <v>7792006000124</v>
       </c>
       <c r="M13" t="s">
@@ -2933,10 +3982,10 @@
       <c r="J14" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="17">
         <v>7792006000124</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="17">
         <v>7792006000124</v>
       </c>
       <c r="M14" t="s">
@@ -3019,10 +4068,10 @@
       <c r="J15" t="s">
         <v>113</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="17">
         <v>7798083661180</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="17">
         <v>7798083661180</v>
       </c>
       <c r="M15" t="s">
@@ -3105,10 +4154,10 @@
       <c r="J16" t="s">
         <v>115</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="17">
         <v>7798083661357</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="17">
         <v>7798083661357</v>
       </c>
       <c r="M16" t="s">
@@ -3191,10 +4240,10 @@
       <c r="J17" t="s">
         <v>117</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17" s="17">
         <v>7798083661487</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="17">
         <v>7798083661487</v>
       </c>
       <c r="M17" t="s">
@@ -3277,10 +4326,10 @@
       <c r="J18" t="s">
         <v>119</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="17">
         <v>7798083661494</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="17">
         <v>7798083661494</v>
       </c>
       <c r="M18" t="s">
@@ -3363,10 +4412,10 @@
       <c r="J19" t="s">
         <v>121</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="17">
         <v>7798083661159</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="17">
         <v>7798083661159</v>
       </c>
       <c r="M19" t="s">
@@ -3449,10 +4498,10 @@
       <c r="J20" t="s">
         <v>123</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="17">
         <v>7798083661166</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="17">
         <v>7798083661166</v>
       </c>
       <c r="M20" t="s">
@@ -3535,10 +4584,10 @@
       <c r="J21" t="s">
         <v>125</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="17">
         <v>7798083661326</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="17">
         <v>7798083661326</v>
       </c>
       <c r="M21" t="s">
@@ -3621,10 +4670,10 @@
       <c r="J22" t="s">
         <v>127</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="17">
         <v>7798083661289</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="17">
         <v>7798083661289</v>
       </c>
       <c r="M22" t="s">
@@ -3707,10 +4756,10 @@
       <c r="J23" t="s">
         <v>129</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="17">
         <v>7798083661388</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="17">
         <v>7798083661388</v>
       </c>
       <c r="M23" t="s">
@@ -3793,10 +4842,10 @@
       <c r="J24" t="s">
         <v>131</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="17">
         <v>7798083661227</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="17">
         <v>7798083661227</v>
       </c>
       <c r="M24" t="s">
@@ -3879,10 +4928,10 @@
       <c r="J25" t="s">
         <v>133</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="17">
         <v>7798083661470</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="17">
         <v>7798083661470</v>
       </c>
       <c r="M25" t="s">
@@ -3965,10 +5014,10 @@
       <c r="J26" t="s">
         <v>135</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="17">
         <v>7792006000209</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="17">
         <v>7792006000209</v>
       </c>
       <c r="M26" t="s">
@@ -4051,10 +5100,10 @@
       <c r="J27" t="s">
         <v>137</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="17">
         <v>7792006000049</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="17">
         <v>7792006000049</v>
       </c>
       <c r="M27" t="s">
@@ -4137,10 +5186,10 @@
       <c r="J28" t="s">
         <v>139</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="17">
         <v>7798083661197</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28" s="17">
         <v>7798083661197</v>
       </c>
       <c r="M28" t="s">
@@ -4223,10 +5272,10 @@
       <c r="J29" t="s">
         <v>141</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="17">
         <v>7798083661203</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="17">
         <v>7798083661203</v>
       </c>
       <c r="M29" t="s">
@@ -4309,10 +5358,10 @@
       <c r="J30" t="s">
         <v>143</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="17" t="s">
         <v>142</v>
       </c>
       <c r="M30" t="s">
@@ -4395,10 +5444,10 @@
       <c r="J31" t="s">
         <v>145</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="17" t="s">
         <v>144</v>
       </c>
       <c r="M31" t="s">
@@ -4481,10 +5530,10 @@
       <c r="J32" t="s">
         <v>147</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="L32" s="17" t="s">
         <v>146</v>
       </c>
       <c r="M32" t="s">
@@ -4567,10 +5616,10 @@
       <c r="J33" t="s">
         <v>149</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="L33" s="17" t="s">
         <v>148</v>
       </c>
       <c r="M33" t="s">
@@ -4653,10 +5702,10 @@
       <c r="J34" t="s">
         <v>151</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K34" s="17">
         <v>7791354000268</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="17">
         <v>7791354000268</v>
       </c>
       <c r="M34" t="s">
@@ -4739,10 +5788,10 @@
       <c r="J35" t="s">
         <v>153</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="17">
         <v>7791354000264</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="17">
         <v>7791354000264</v>
       </c>
       <c r="M35" t="s">
@@ -4804,4 +5853,1616 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:F165"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="34.7142857142857" style="1"/>
+    <col min="2" max="3" width="23.7142857142857" style="1"/>
+    <col min="4" max="4" width="60.4285714285714" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7142857142857" style="2"/>
+    <col min="6" max="6" width="13.5714285714286" style="2"/>
+    <col min="7" max="16384" width="9.14285714285714" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="15" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="8">
+        <f>ROWS('maestro '!B2:BW35)</f>
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="8">
+        <f>COLUMNS('maestro '!B1:BX36)</f>
+        <v>75</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="8">
+        <f>C4*C3</f>
+        <v>2550</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="8">
+        <f>COUNTBLANK('maestro '!A2:BW35)</f>
+        <v>1598</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="8">
+        <f>C5-C6</f>
+        <v>952</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:4">
+      <c r="A8" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="10">
+        <f>C7/C5</f>
+        <v>0.373333333333333</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:4">
+      <c r="A13" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:4">
+      <c r="A14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:4">
+      <c r="A15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:4">
+      <c r="A16" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:6">
+      <c r="A17" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:6">
+      <c r="A18" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:6">
+      <c r="A19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:6">
+      <c r="A20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:6">
+      <c r="A21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:6">
+      <c r="A22" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:6">
+      <c r="A23" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:6">
+      <c r="A24" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:6">
+      <c r="A25" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:6">
+      <c r="A26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:6">
+      <c r="A27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:6">
+      <c r="A28" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:6">
+      <c r="A29" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:6">
+      <c r="A30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:6">
+      <c r="A31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:6">
+      <c r="A32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32"/>
+    </row>
+    <row r="33" ht="15" spans="1:6">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+    </row>
+    <row r="34" ht="15" spans="1:6">
+      <c r="A34" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+    </row>
+    <row r="35" ht="15" spans="1:6">
+      <c r="A35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+    </row>
+    <row r="36" ht="15" spans="1:6">
+      <c r="A36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" ht="15" spans="1:6">
+      <c r="A37" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+    </row>
+    <row r="38" ht="15" spans="1:6">
+      <c r="A38" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+    </row>
+    <row r="39" ht="15" spans="1:6">
+      <c r="A39" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+    </row>
+    <row r="40" ht="15" spans="1:6">
+      <c r="A40" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" ht="15" spans="1:6">
+      <c r="A41" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
+        <v>194</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+    </row>
+    <row r="42" ht="15" spans="1:6">
+      <c r="A42" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+    </row>
+    <row r="43" ht="15" spans="1:6">
+      <c r="A43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+    </row>
+    <row r="44" ht="15" spans="1:6">
+      <c r="A44" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+    </row>
+    <row r="45" ht="15" spans="1:6">
+      <c r="A45" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="1:6">
+      <c r="A46" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="1:6">
+      <c r="A47" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D47" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="1:6">
+      <c r="A48" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="1:4">
+      <c r="A49" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="1:4">
+      <c r="A50" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="1:4">
+      <c r="A51" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="1:4">
+      <c r="A52" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="1:4">
+      <c r="A53" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="1:4">
+      <c r="A54" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:4">
+      <c r="A55" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="1:4">
+      <c r="A56" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" ht="15" spans="1:4">
+      <c r="A57" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" ht="15" spans="1:4">
+      <c r="A58" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" ht="15" spans="1:4">
+      <c r="A59" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" ht="15" spans="1:4">
+      <c r="A60" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="61" ht="15" spans="1:4">
+      <c r="A61" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" ht="15" spans="1:4">
+      <c r="A62" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" ht="15" spans="1:4">
+      <c r="A63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="64" ht="15" spans="1:4">
+      <c r="A64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" ht="15" spans="1:4">
+      <c r="A65" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" ht="15" spans="1:4">
+      <c r="A66" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:4">
+      <c r="A67" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" ht="15" spans="1:4">
+      <c r="A68" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" t="s">
+        <v>199</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" ht="15" spans="1:4">
+      <c r="A69" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" ht="15" spans="1:4">
+      <c r="A70" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" ht="15" spans="1:4">
+      <c r="A71" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B71" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" ht="15" spans="1:4">
+      <c r="A72" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" ht="15" spans="1:4">
+      <c r="A73" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" ht="15" spans="1:4">
+      <c r="A74" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" ht="15" spans="1:4">
+      <c r="A75" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" ht="15" spans="1:4">
+      <c r="A76" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="77" ht="15" spans="1:4">
+      <c r="A77" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" t="s">
+        <v>199</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="78" ht="15" spans="1:4">
+      <c r="A78" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79" ht="15" spans="1:4">
+      <c r="A79" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" ht="15" spans="1:4">
+      <c r="A80" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" ht="15" spans="1:6">
+      <c r="A81" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" ht="15" spans="1:6">
+      <c r="A82" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B82" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" ht="15" spans="1:6">
+      <c r="A83" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" ht="15" spans="1:6">
+      <c r="A84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" t="s">
+        <v>197</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85" ht="15" spans="1:6">
+      <c r="A85" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D85" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="86" ht="15" spans="1:6">
+      <c r="A86" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87" ht="15" spans="1:6">
+      <c r="A87" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" t="s">
+        <v>188</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" ht="15" spans="1:6">
+      <c r="A90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+    </row>
+    <row r="91" ht="15" spans="1:6">
+      <c r="A91" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" t="s">
+        <v>186</v>
+      </c>
+      <c r="F91" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" ht="15" spans="1:6">
+      <c r="A92" t="s">
+        <v>199</v>
+      </c>
+      <c r="B92"/>
+      <c r="C92">
+        <v>20</v>
+      </c>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" ht="15" spans="1:6">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93">
+        <v>9</v>
+      </c>
+      <c r="E93"/>
+      <c r="F93">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" ht="15" spans="1:6">
+      <c r="A94" t="s">
+        <v>195</v>
+      </c>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94">
+        <v>5</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" ht="15" spans="1:6">
+      <c r="A95" t="s">
+        <v>180</v>
+      </c>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95">
+        <v>7</v>
+      </c>
+      <c r="E95"/>
+      <c r="F95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" ht="15" spans="1:6">
+      <c r="A96" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96">
+        <v>5</v>
+      </c>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" ht="15" spans="1:6">
+      <c r="A97" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97">
+        <v>11</v>
+      </c>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" ht="15" spans="1:6">
+      <c r="A98" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="F98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" ht="15" spans="1:6">
+      <c r="A99" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99">
+        <v>7</v>
+      </c>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" ht="15" spans="1:6">
+      <c r="A100" t="s">
+        <v>193</v>
+      </c>
+      <c r="B100">
+        <v>8</v>
+      </c>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" ht="15" spans="1:6">
+      <c r="A101" t="s">
+        <v>203</v>
+      </c>
+      <c r="B101">
+        <v>31</v>
+      </c>
+      <c r="C101">
+        <v>20</v>
+      </c>
+      <c r="D101">
+        <v>16</v>
+      </c>
+      <c r="E101">
+        <v>8</v>
+      </c>
+      <c r="F101">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" ht="15" spans="1:6">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+    </row>
+    <row r="103" ht="15" spans="1:6">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+    </row>
+    <row r="104" ht="15" spans="1:6">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+    </row>
+    <row r="105" ht="15" spans="1:6">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+    </row>
+    <row r="106" ht="15" spans="1:6">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+    </row>
+    <row r="107" ht="15" spans="1:6">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+    </row>
+    <row r="108" ht="15" spans="1:6">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+    </row>
+    <row r="109" ht="15" spans="1:6">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+    </row>
+    <row r="110" ht="15" spans="1:6">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+    </row>
+    <row r="111" ht="15" spans="1:6">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" ht="15" spans="1:6">
+      <c r="A112"/>
+    </row>
+    <row r="113" ht="15" spans="1:1">
+      <c r="A113"/>
+    </row>
+    <row r="114" ht="15" spans="1:1">
+      <c r="A114"/>
+    </row>
+    <row r="115" ht="15" spans="1:1">
+      <c r="A115"/>
+    </row>
+    <row r="116" ht="15" spans="1:1">
+      <c r="A116"/>
+    </row>
+    <row r="117" ht="15" spans="1:1">
+      <c r="A117"/>
+    </row>
+    <row r="118" ht="15" spans="1:1">
+      <c r="A118"/>
+    </row>
+    <row r="119" ht="15" spans="1:1">
+      <c r="A119"/>
+    </row>
+    <row r="120" ht="15" spans="1:1">
+      <c r="A120"/>
+    </row>
+    <row r="121" ht="15" spans="1:1">
+      <c r="A121"/>
+    </row>
+    <row r="122" ht="15" spans="1:1">
+      <c r="A122"/>
+    </row>
+    <row r="123" ht="15" spans="1:1">
+      <c r="A123"/>
+    </row>
+    <row r="124" ht="15" spans="1:1">
+      <c r="A124"/>
+    </row>
+    <row r="125" ht="15" spans="1:1">
+      <c r="A125"/>
+    </row>
+    <row r="126" ht="15" spans="1:1">
+      <c r="A126"/>
+    </row>
+    <row r="127" ht="15" spans="1:1">
+      <c r="A127"/>
+    </row>
+    <row r="128" ht="15" spans="1:1">
+      <c r="A128"/>
+    </row>
+    <row r="129" ht="15" spans="1:1">
+      <c r="A129"/>
+    </row>
+    <row r="130" ht="15" spans="1:1">
+      <c r="A130"/>
+    </row>
+    <row r="131" ht="15" spans="1:1">
+      <c r="A131"/>
+    </row>
+    <row r="132" ht="15" spans="1:1">
+      <c r="A132"/>
+    </row>
+    <row r="133" ht="15" spans="1:1">
+      <c r="A133"/>
+    </row>
+    <row r="134" ht="15" spans="1:1">
+      <c r="A134"/>
+    </row>
+    <row r="135" ht="15" spans="1:1">
+      <c r="A135"/>
+    </row>
+    <row r="136" ht="15" spans="1:1">
+      <c r="A136"/>
+    </row>
+    <row r="137" ht="15" spans="1:1">
+      <c r="A137"/>
+    </row>
+    <row r="138" ht="15" spans="1:1">
+      <c r="A138"/>
+    </row>
+    <row r="139" ht="15" spans="1:1">
+      <c r="A139"/>
+    </row>
+    <row r="140" ht="15" spans="1:1">
+      <c r="A140"/>
+    </row>
+    <row r="141" ht="15" spans="1:1">
+      <c r="A141"/>
+    </row>
+    <row r="142" ht="15" spans="1:1">
+      <c r="A142"/>
+    </row>
+    <row r="143" ht="15" spans="1:1">
+      <c r="A143"/>
+    </row>
+    <row r="144" ht="15" spans="1:1">
+      <c r="A144"/>
+    </row>
+    <row r="145" ht="15" spans="1:1">
+      <c r="A145"/>
+    </row>
+    <row r="146" ht="15" spans="1:1">
+      <c r="A146"/>
+    </row>
+    <row r="147" ht="15" spans="1:1">
+      <c r="A147"/>
+    </row>
+    <row r="148" ht="15" spans="1:1">
+      <c r="A148"/>
+    </row>
+    <row r="149" ht="15" spans="1:1">
+      <c r="A149"/>
+    </row>
+    <row r="150" ht="15" spans="1:1">
+      <c r="A150"/>
+    </row>
+    <row r="151" ht="15" spans="1:1">
+      <c r="A151"/>
+    </row>
+    <row r="152" ht="15" spans="1:1">
+      <c r="A152"/>
+    </row>
+    <row r="153" ht="15" spans="1:1">
+      <c r="A153"/>
+    </row>
+    <row r="154" ht="15" spans="1:1">
+      <c r="A154"/>
+    </row>
+    <row r="155" ht="15" spans="1:1">
+      <c r="A155"/>
+    </row>
+    <row r="156" ht="15" spans="1:1">
+      <c r="A156"/>
+    </row>
+    <row r="157" ht="15" spans="1:1">
+      <c r="A157"/>
+    </row>
+    <row r="158" ht="15" spans="1:1">
+      <c r="A158"/>
+    </row>
+    <row r="159" ht="15" spans="1:1">
+      <c r="A159"/>
+    </row>
+    <row r="160" ht="15" spans="1:1">
+      <c r="A160"/>
+    </row>
+    <row r="161" ht="15" spans="1:1">
+      <c r="A161"/>
+    </row>
+    <row r="162" ht="15" spans="1:1">
+      <c r="A162"/>
+    </row>
+    <row r="163" ht="15" spans="1:1">
+      <c r="A163"/>
+    </row>
+    <row r="164" ht="15" spans="1:1">
+      <c r="A164"/>
+    </row>
+    <row r="165" ht="15" spans="1:1">
+      <c r="A165"/>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A12:D87" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>